--- a/data/trans_dic/IP2001-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP2001-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que tienen caries</t>
+          <t>Menores que tienen caries (tasa de respuesta: 99,49%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,36; 8,16</t>
+          <t>1,34; 7,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,17; 10,52</t>
+          <t>1,89; 10,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,64; 15,11</t>
+          <t>3,95; 15,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,65; 9,35</t>
+          <t>2,64; 10,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,05; 12,18</t>
+          <t>3,07; 11,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,88</t>
+          <t>0,0; 5,81</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,24; 14,94</t>
+          <t>4,69; 15,51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,69; 9,65</t>
+          <t>2,8; 9,71</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,66; 8,2</t>
+          <t>2,71; 7,61</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,44; 6,04</t>
+          <t>1,44; 6,51</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,96; 12,77</t>
+          <t>5,35; 13,42</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,46; 8,68</t>
+          <t>3,44; 8,45</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,25; 9,11</t>
+          <t>0,86; 8,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,75; 13,84</t>
+          <t>3,67; 13,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,38; 13,08</t>
+          <t>4,01; 12,61</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,94</t>
+          <t>0,0; 5,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,29; 12,83</t>
+          <t>3,29; 12,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,02; 8,46</t>
+          <t>1,43; 8,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,58; 12,26</t>
+          <t>3,98; 12,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,74; 13,92</t>
+          <t>2,56; 12,57</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,81; 9,15</t>
+          <t>2,82; 8,56</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,36; 9,61</t>
+          <t>3,44; 9,43</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,78; 10,83</t>
+          <t>5,1; 11,3</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,78; 7,8</t>
+          <t>1,79; 7,75</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,65; 15,5</t>
+          <t>3,76; 16,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,82; 20,4</t>
+          <t>7,75; 19,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,15; 13,84</t>
+          <t>3,07; 13,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,43; 14,84</t>
+          <t>2,61; 14,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,0; 9,8</t>
+          <t>1,94; 9,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,06; 15,84</t>
+          <t>5,73; 15,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,02; 10,96</t>
+          <t>1,97; 11,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,58</t>
+          <t>0,0; 8,8</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,57; 9,37</t>
+          <t>3,41; 9,98</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,38; 16,02</t>
+          <t>7,67; 15,55</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,41; 10,44</t>
+          <t>3,46; 10,53</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,7; 8,57</t>
+          <t>1,7; 8,03</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,3; 12,63</t>
+          <t>6,22; 12,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,23; 12,97</t>
+          <t>6,5; 13,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,8; 17,34</t>
+          <t>10,1; 17,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,72; 8,34</t>
+          <t>2,84; 8,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,16; 14,23</t>
+          <t>6,88; 14,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,14; 11,62</t>
+          <t>4,99; 11,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,24; 14,3</t>
+          <t>7,28; 14,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,37; 11,29</t>
+          <t>4,43; 11,13</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,57; 12,3</t>
+          <t>7,61; 12,26</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,31; 11,23</t>
+          <t>6,47; 11,12</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,53; 15,1</t>
+          <t>9,41; 14,69</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,2; 8,64</t>
+          <t>4,24; 8,53</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,53; 18,41</t>
+          <t>7,57; 17,84</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,09; 19,19</t>
+          <t>8,89; 18,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,28; 17,79</t>
+          <t>8,2; 17,97</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,89; 8,06</t>
+          <t>1,89; 8,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,78; 15,7</t>
+          <t>6,65; 15,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,6; 21,13</t>
+          <t>10,4; 21,36</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,78; 22,48</t>
+          <t>11,52; 22,58</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,23; 10,78</t>
+          <t>3,11; 10,49</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,54; 15,24</t>
+          <t>8,11; 14,59</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11,15; 18,5</t>
+          <t>11,01; 17,94</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11,05; 17,99</t>
+          <t>11,05; 18,32</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,18; 8,31</t>
+          <t>3,17; 8,41</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,74; 10,27</t>
+          <t>1,76; 10,39</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,86</t>
+          <t>0,0; 8,39</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,2; 12,43</t>
+          <t>2,08; 11,47</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,59</t>
+          <t>0,0; 7,27</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,95</t>
+          <t>0,0; 6,03</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,98; 20,62</t>
+          <t>6,42; 20,19</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,88; 7,89</t>
+          <t>0,86; 7,93</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,7; 11,89</t>
+          <t>0,7; 12,15</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,47; 6,66</t>
+          <t>1,5; 6,69</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4,74; 13,56</t>
+          <t>4,76; 13,71</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,98; 7,55</t>
+          <t>2,03; 8,32</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,13; 7,3</t>
+          <t>0,95; 6,83</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,87; 9,23</t>
+          <t>5,78; 9,39</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,63; 11,42</t>
+          <t>7,57; 11,39</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,56; 12,49</t>
+          <t>8,65; 12,65</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,07; 5,78</t>
+          <t>3,07; 5,74</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,04; 9,41</t>
+          <t>6,01; 9,3</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,94; 10,79</t>
+          <t>7,13; 10,92</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,01; 11,8</t>
+          <t>7,95; 11,71</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,26; 7,53</t>
+          <t>4,35; 7,47</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,43; 8,81</t>
+          <t>6,4; 8,77</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7,86; 10,57</t>
+          <t>7,63; 10,36</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8,68; 11,53</t>
+          <t>8,83; 11,63</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,13; 6,23</t>
+          <t>4,02; 6,36</t>
         </is>
       </c>
     </row>
@@ -1638,4 +1639,1622 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que tienen caries (tasa de respuesta: 99,49%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>3503</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4124</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6342</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>5735</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>5807</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1302</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>7792</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>7398</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>9310</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>5426</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>14135</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>13133</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>1290; 7604</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1574; 8355</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3052; 11601</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2710; 10432</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2812; 10850</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4759</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>4232; 13982</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>3810; 13215</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>5091; 14318</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2376; 10750</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>8959; 22471</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>8216; 20190</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>3003</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>6644</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>7696</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1441</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>5437</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>3879</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>7606</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>5787</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>8440</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>10524</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>15302</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>7228</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>694; 7269</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>3187; 11798</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>3914; 12317</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5401</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2709; 10359</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1312; 7875</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>4195; 12974</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>2387; 11722</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>4606; 13985</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>6154; 16867</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>10371; 22967</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>3372; 14565</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>5438</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>10291</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4313</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>3642</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>4542</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>7954</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>4092</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>955</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>9980</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>18246</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>8406</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>4597</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2377; 10406</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>6255; 15704</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1796; 8099</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1305; 7243</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1899; 9076</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>4710; 12952</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>1398; 8347</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5559</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>5498; 16081</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>12505; 25350</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>4472; 13620</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>1922; 9080</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>17566</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>17542</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>27899</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>10732</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>19374</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>16663</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>21608</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>15427</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>36940</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>34204</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>49508</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>26159</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>11925; 24862</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>12367; 25358</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>20981; 35914</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>6072; 17875</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>12821; 26946</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>10514; 23852</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>14744; 29364</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>9357; 23505</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>28757; 46315</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>25948; 44571</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>38585; 60287</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>18016; 36261</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>11940</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>18065</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>16089</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>12490</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>20024</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>22141</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>9614</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>24430</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>38089</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>38230</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>14615</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>7531; 17761</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>12086; 25153</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>10697; 23437</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>2206; 10064</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>7875; 18532</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>13621; 27965</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>15490; 30362</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>4959; 16736</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>17678; 31815</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>29375; 47862</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>29280; 48517</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>8755; 23232</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>3301</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1353</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>3191</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1358</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1298</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>8487</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>1917</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>2876</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>4599</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>9841</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>5108</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>4234</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>1257; 7428</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4133</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>1182; 6503</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>0; 5011</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3919</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>4333; 13625</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>562; 5156</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>493; 8559</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>2047; 9134</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>5558; 16003</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>2476; 10120</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>1324; 9512</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>44752</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>58020</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>65531</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>27909</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>48948</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>58309</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>65157</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>42057</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>93699</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>116329</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>130688</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>69965</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>34879; 56649</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>47404; 71340</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>54373; 79467</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>19879; 37163</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>38547; 59644</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>47422; 72645</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>53125; 78278</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>31907; 54798</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>79622; 109168</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>98537; 133788</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>114478; 150783</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>55536; 87740</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP2001-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP2001-Clase-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,34; 7,89</t>
+          <t>1,28; 8,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,89; 10,03</t>
+          <t>1,73; 9,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,95; 15,02</t>
+          <t>3,53; 14,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,64; 10,14</t>
+          <t>2,85; 9,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,07; 11,84</t>
+          <t>3,02; 11,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,81</t>
+          <t>0,0; 5,71</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,69; 15,51</t>
+          <t>4,39; 14,9</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,8; 9,71</t>
+          <t>2,59; 9,64</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,71; 7,61</t>
+          <t>2,79; 8,03</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,44; 6,51</t>
+          <t>1,6; 6,35</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,35; 13,42</t>
+          <t>5,46; 12,88</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,44; 8,45</t>
+          <t>3,57; 8,36</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,86; 8,97</t>
+          <t>0,85; 8,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,67; 13,6</t>
+          <t>3,34; 13,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,01; 12,61</t>
+          <t>4,4; 13,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,7</t>
+          <t>0,0; 4,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,29; 12,57</t>
+          <t>3,18; 12,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,43; 8,55</t>
+          <t>2,01; 8,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,98; 12,29</t>
+          <t>3,92; 12,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,56; 12,57</t>
+          <t>2,73; 13,88</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,82; 8,56</t>
+          <t>2,84; 8,57</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,44; 9,43</t>
+          <t>3,47; 9,11</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,1; 11,3</t>
+          <t>4,95; 11,02</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,79; 7,75</t>
+          <t>1,81; 7,34</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,76; 16,44</t>
+          <t>4,05; 15,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,75; 19,45</t>
+          <t>7,78; 20,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,07; 13,85</t>
+          <t>3,14; 13,98</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,61; 14,51</t>
+          <t>3,1; 14,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,94; 9,28</t>
+          <t>1,97; 9,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,73; 15,75</t>
+          <t>5,22; 15,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,97; 11,79</t>
+          <t>2,75; 12,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,8</t>
+          <t>0,0; 9,53</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,41; 9,98</t>
+          <t>3,57; 10,11</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,67; 15,55</t>
+          <t>7,61; 15,75</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,46; 10,53</t>
+          <t>3,5; 10,88</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,7; 8,03</t>
+          <t>1,9; 9,14</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,22; 12,97</t>
+          <t>6,4; 12,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,5; 13,32</t>
+          <t>5,99; 12,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,1; 17,29</t>
+          <t>9,92; 17,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,84; 8,35</t>
+          <t>2,62; 8,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,88; 14,47</t>
+          <t>7,16; 14,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,99; 11,32</t>
+          <t>4,97; 11,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,28; 14,5</t>
+          <t>7,31; 14,45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,43; 11,13</t>
+          <t>4,51; 11,05</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,61; 12,26</t>
+          <t>7,43; 12,37</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,47; 11,12</t>
+          <t>6,6; 11,35</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,41; 14,69</t>
+          <t>9,83; 15,27</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,24; 8,53</t>
+          <t>4,09; 8,67</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,57; 17,84</t>
+          <t>7,42; 18,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,89; 18,5</t>
+          <t>9,07; 18,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,2; 17,97</t>
+          <t>8,43; 17,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,89; 8,63</t>
+          <t>1,78; 8,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,65; 15,65</t>
+          <t>6,35; 15,71</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,4; 21,36</t>
+          <t>10,46; 21,66</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,52; 22,58</t>
+          <t>11,57; 22,44</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,11; 10,49</t>
+          <t>2,97; 10,56</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,11; 14,59</t>
+          <t>8,18; 15,05</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11,01; 17,94</t>
+          <t>11,12; 18,5</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11,05; 18,32</t>
+          <t>10,62; 18,06</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,17; 8,41</t>
+          <t>3,09; 8,25</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,76; 10,39</t>
+          <t>1,72; 9,68</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,39</t>
+          <t>0,0; 9,65</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,08; 11,47</t>
+          <t>2,08; 11,77</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,27</t>
+          <t>0,0; 6,75</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,03</t>
+          <t>0,0; 7,04</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,42; 20,19</t>
+          <t>6,85; 19,79</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,86; 7,93</t>
+          <t>0,87; 8,07</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,7; 12,15</t>
+          <t>0,71; 13,12</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,5; 6,69</t>
+          <t>1,43; 6,41</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4,76; 13,71</t>
+          <t>4,63; 13,32</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,03; 8,32</t>
+          <t>2,0; 8,54</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,95; 6,83</t>
+          <t>1,14; 7,29</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,78; 9,39</t>
+          <t>5,78; 9,35</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,57; 11,39</t>
+          <t>7,34; 11,16</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,65; 12,65</t>
+          <t>8,62; 12,53</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,07; 5,74</t>
+          <t>3,12; 5,86</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,01; 9,3</t>
+          <t>6,17; 9,58</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,13; 10,92</t>
+          <t>7,09; 10,6</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,95; 11,71</t>
+          <t>8,02; 11,76</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,35; 7,47</t>
+          <t>4,27; 7,82</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,4; 8,77</t>
+          <t>6,3; 8,68</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7,63; 10,36</t>
+          <t>7,69; 10,34</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8,83; 11,63</t>
+          <t>8,78; 11,47</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,02; 6,36</t>
+          <t>4,05; 6,35</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1290; 7604</t>
+          <t>1229; 8036</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1574; 8355</t>
+          <t>1440; 8043</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3052; 11601</t>
+          <t>2724; 11530</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2710; 10432</t>
+          <t>2926; 9893</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2812; 10850</t>
+          <t>2772; 10454</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4759</t>
+          <t>0; 4678</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4232; 13982</t>
+          <t>3958; 13432</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3810; 13215</t>
+          <t>3521; 13120</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5091; 14318</t>
+          <t>5255; 15093</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2376; 10750</t>
+          <t>2647; 10487</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8959; 22471</t>
+          <t>9136; 21553</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8216; 20190</t>
+          <t>8528; 19982</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>694; 7269</t>
+          <t>691; 6756</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3187; 11798</t>
+          <t>2898; 11536</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3914; 12317</t>
+          <t>4302; 13136</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 5401</t>
+          <t>0; 4639</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2709; 10359</t>
+          <t>2619; 10114</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1312; 7875</t>
+          <t>1852; 7868</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4195; 12974</t>
+          <t>4132; 12672</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2387; 11722</t>
+          <t>2545; 12941</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4606; 13985</t>
+          <t>4638; 14002</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6154; 16867</t>
+          <t>6198; 16297</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10371; 22967</t>
+          <t>10066; 22393</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3372; 14565</t>
+          <t>3410; 13790</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2377; 10406</t>
+          <t>2565; 9702</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6255; 15704</t>
+          <t>6282; 16394</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1796; 8099</t>
+          <t>1835; 8178</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1305; 7243</t>
+          <t>1550; 7283</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1899; 9076</t>
+          <t>1926; 8977</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4710; 12952</t>
+          <t>4291; 12786</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1398; 8347</t>
+          <t>1947; 8779</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 5559</t>
+          <t>0; 6015</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5498; 16081</t>
+          <t>5751; 16280</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12505; 25350</t>
+          <t>12402; 25676</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4472; 13620</t>
+          <t>4522; 14070</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1922; 9080</t>
+          <t>2150; 10334</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11925; 24862</t>
+          <t>12270; 24850</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12367; 25358</t>
+          <t>11396; 24047</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20981; 35914</t>
+          <t>20620; 37003</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6072; 17875</t>
+          <t>5616; 17270</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12821; 26946</t>
+          <t>13325; 27108</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10514; 23852</t>
+          <t>10476; 23931</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14744; 29364</t>
+          <t>14803; 29262</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9357; 23505</t>
+          <t>9532; 23319</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>28757; 46315</t>
+          <t>28068; 46755</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>25948; 44571</t>
+          <t>26460; 45501</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>38585; 60287</t>
+          <t>40316; 62642</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>18016; 36261</t>
+          <t>17400; 36840</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>7531; 17761</t>
+          <t>7387; 18555</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>12086; 25153</t>
+          <t>12331; 24861</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10697; 23437</t>
+          <t>10999; 22773</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2206; 10064</t>
+          <t>2081; 10033</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>7875; 18532</t>
+          <t>7517; 18610</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13621; 27965</t>
+          <t>13689; 28355</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15490; 30362</t>
+          <t>15554; 30171</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>4959; 16736</t>
+          <t>4739; 16843</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>17678; 31815</t>
+          <t>17839; 32800</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>29375; 47862</t>
+          <t>29681; 49371</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>29280; 48517</t>
+          <t>28129; 47835</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>8755; 23232</t>
+          <t>8529; 22786</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1257; 7428</t>
+          <t>1227; 6924</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 4133</t>
+          <t>0; 4753</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1182; 6503</t>
+          <t>1180; 6673</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 5011</t>
+          <t>0; 4648</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 3919</t>
+          <t>0; 4578</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4333; 13625</t>
+          <t>4622; 13358</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>562; 5156</t>
+          <t>565; 5245</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>493; 8559</t>
+          <t>501; 9245</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2047; 9134</t>
+          <t>1955; 8755</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5558; 16003</t>
+          <t>5404; 15548</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2476; 10120</t>
+          <t>2437; 10392</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1324; 9512</t>
+          <t>1583; 10161</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>34879; 56649</t>
+          <t>34878; 56454</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>47404; 71340</t>
+          <t>45977; 69901</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>54373; 79467</t>
+          <t>54181; 78750</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>19879; 37163</t>
+          <t>20193; 37938</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>38547; 59644</t>
+          <t>39571; 61459</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>47422; 72645</t>
+          <t>47139; 70518</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>53125; 78278</t>
+          <t>53596; 78633</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>31907; 54798</t>
+          <t>31290; 57353</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>79622; 109168</t>
+          <t>78403; 108127</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>98537; 133788</t>
+          <t>99347; 133515</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>114478; 150783</t>
+          <t>113883; 148752</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>55536; 87740</t>
+          <t>55902; 87706</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP2001-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP2001-Clase-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6,34%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8,64%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5,58%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>3,63%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>4,95%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>8,21%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5,58%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>6,34%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,59%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>8,64%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,48%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,28; 8,34</t>
+          <t>3,05; 12,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,73; 9,65</t>
+          <t>0,0; 4,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,53; 14,92</t>
+          <t>4,24; 14,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,85; 9,62</t>
+          <t>2,83; 10,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,02; 11,41</t>
+          <t>1,36; 8,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,71</t>
+          <t>2,17; 10,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,39; 14,9</t>
+          <t>3,64; 15,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,59; 9,64</t>
+          <t>2,6; 9,35</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,79; 8,03</t>
+          <t>2,66; 8,2</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,6; 6,35</t>
+          <t>1,44; 6,04</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,46; 12,88</t>
+          <t>4,96; 12,77</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,57; 8,36</t>
+          <t>3,37; 8,53</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>6,6%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4,21%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>7,21%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>6,58%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>3,71%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>7,66%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>7,88%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>6,6%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>4,21%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>7,21%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,85; 8,34</t>
+          <t>3,29; 12,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,34; 13,3</t>
+          <t>2,02; 8,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,4; 13,45</t>
+          <t>3,58; 12,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,9</t>
+          <t>3,12; 14,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,18; 12,28</t>
+          <t>1,25; 9,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,01; 8,55</t>
+          <t>3,75; 13,84</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,92; 12,01</t>
+          <t>4,38; 13,08</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,73; 13,88</t>
+          <t>0,0; 4,37</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,84; 8,57</t>
+          <t>2,81; 9,15</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,47; 9,11</t>
+          <t>3,36; 9,61</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,95; 11,02</t>
+          <t>4,78; 10,83</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,81; 7,34</t>
+          <t>1,8; 7,54</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>4,64%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9,67%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5,78%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1,7%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>8,59%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>12,75%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>7,37%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>7,29%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>4,64%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>9,67%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>5,78%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,05; 15,33</t>
+          <t>2,0; 9,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,78; 20,3</t>
+          <t>5,06; 15,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,14; 13,98</t>
+          <t>2,02; 10,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,1; 14,59</t>
+          <t>0,0; 8,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,97; 9,18</t>
+          <t>3,65; 15,5</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,22; 15,54</t>
+          <t>7,82; 20,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,75; 12,4</t>
+          <t>3,15; 13,84</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,53</t>
+          <t>2,29; 14,42</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,57; 10,11</t>
+          <t>3,57; 9,37</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,61; 15,75</t>
+          <t>7,38; 16,02</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,5; 10,88</t>
+          <t>3,41; 10,44</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,9; 9,14</t>
+          <t>1,67; 8,53</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>10,4%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7,91%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>10,67%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7,52%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>9,16%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>9,22%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>13,43%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5,02%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>10,4%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7,91%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>10,67%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,4; 12,97</t>
+          <t>7,16; 14,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,99; 12,63</t>
+          <t>5,14; 11,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,92; 17,81</t>
+          <t>7,24; 14,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,62; 8,07</t>
+          <t>4,47; 11,58</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,16; 14,56</t>
+          <t>6,3; 12,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,97; 11,36</t>
+          <t>6,23; 12,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,31; 14,45</t>
+          <t>9,8; 17,34</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,51; 11,05</t>
+          <t>3,73; 9,83</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,43; 12,37</t>
+          <t>7,57; 12,3</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,6; 11,35</t>
+          <t>6,31; 11,23</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,83; 15,27</t>
+          <t>9,53; 15,1</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,09; 8,67</t>
+          <t>4,95; 9,6</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>10,55%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>15,3%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>16,47%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>6,35%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>11,99%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>13,29%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>12,34%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>4,29%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>10,55%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>15,3%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>16,47%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,42; 18,64</t>
+          <t>6,78; 15,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,07; 18,29</t>
+          <t>10,6; 21,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,43; 17,46</t>
+          <t>11,78; 22,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,78; 8,6</t>
+          <t>3,37; 11,64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,35; 15,71</t>
+          <t>7,53; 18,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,46; 21,66</t>
+          <t>9,09; 19,19</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,57; 22,44</t>
+          <t>8,28; 17,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,97; 10,56</t>
+          <t>1,99; 8,54</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,18; 15,05</t>
+          <t>8,54; 15,24</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11,12; 18,5</t>
+          <t>11,15; 18,5</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10,62; 18,06</t>
+          <t>11,05; 17,99</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,09; 8,25</t>
+          <t>3,38; 8,9</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2,0%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>12,57%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2,95%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3,36%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>4,62%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>2,75%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>5,63%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1,97%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>12,57%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2,95%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,72; 9,68</t>
+          <t>0,0; 6,95</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,65</t>
+          <t>6,98; 20,62</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,08; 11,77</t>
+          <t>0,88; 7,89</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,75</t>
+          <t>0,89; 9,58</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,04</t>
+          <t>1,74; 10,27</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,85; 19,79</t>
+          <t>0,0; 8,86</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,87; 8,07</t>
+          <t>2,2; 12,43</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,71; 13,12</t>
+          <t>0,0; 7,51</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,43; 6,41</t>
+          <t>1,47; 6,66</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4,63; 13,32</t>
+          <t>4,74; 13,56</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,0; 8,54</t>
+          <t>1,98; 7,55</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,14; 7,29</t>
+          <t>1,05; 6,23</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>7,63%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>8,76%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>9,75%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5,9%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>7,42%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>9,26%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>10,43%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4,31%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>7,63%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>8,76%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>9,75%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,78; 9,35</t>
+          <t>6,04; 9,41</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,34; 11,16</t>
+          <t>6,94; 10,79</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,62; 12,53</t>
+          <t>8,01; 11,8</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,12; 5,86</t>
+          <t>4,42; 7,75</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,17; 9,58</t>
+          <t>5,87; 9,23</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,09; 10,6</t>
+          <t>7,63; 11,42</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,02; 11,76</t>
+          <t>8,56; 12,49</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,27; 7,82</t>
+          <t>3,24; 6,04</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,3; 8,68</t>
+          <t>6,43; 8,81</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7,69; 10,34</t>
+          <t>7,86; 10,57</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8,78; 11,47</t>
+          <t>8,68; 11,53</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,05; 6,35</t>
+          <t>4,27; 6,44</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1791,37 +1791,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -1859,42 +1859,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>5807</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1302</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>7792</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>6807</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>3503</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>4124</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>6342</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>5735</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>5807</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1302</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>7792</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7398</t>
+          <t>5447</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13133</t>
+          <t>12255</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1229; 8036</t>
+          <t>2800; 11167</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1440; 8043</t>
+          <t>0; 3999</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2724; 11530</t>
+          <t>3819; 13466</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2926; 9893</t>
+          <t>3451; 12515</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2772; 10454</t>
+          <t>1309; 7861</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4678</t>
+          <t>1810; 8763</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3958; 13432</t>
+          <t>2815; 11673</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3521; 13120</t>
+          <t>2641; 9495</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5255; 15093</t>
+          <t>5001; 15421</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2647; 10487</t>
+          <t>2373; 9977</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9136; 21553</t>
+          <t>8308; 21369</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8528; 19982</t>
+          <t>7540; 19052</t>
         </is>
       </c>
     </row>
@@ -1999,42 +1999,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2067,42 +2067,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5437</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3879</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>7606</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>5893</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>3003</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>6644</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>7696</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1441</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>5437</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3879</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>7606</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5787</t>
+          <t>1329</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7228</t>
+          <t>7222</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>691; 6756</t>
+          <t>2709; 10572</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2898; 11536</t>
+          <t>1862; 7789</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4302; 13136</t>
+          <t>3773; 12939</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4639</t>
+          <t>2793; 13115</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2619; 10114</t>
+          <t>1017; 7385</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1852; 7868</t>
+          <t>3253; 12009</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4132; 12672</t>
+          <t>4280; 12779</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2545; 12941</t>
+          <t>0; 4223</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4638; 14002</t>
+          <t>4586; 14962</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6198; 16297</t>
+          <t>6002; 17191</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10066; 22393</t>
+          <t>9710; 22014</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3410; 13790</t>
+          <t>3349; 14033</t>
         </is>
       </c>
     </row>
@@ -2207,42 +2207,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2275,42 +2275,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>4542</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>7954</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4092</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>961</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>5438</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>10291</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>4313</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>3642</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>4542</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>7954</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>4092</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>3505</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4597</t>
+          <t>4465</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2565; 9702</t>
+          <t>1960; 9589</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6282; 16394</t>
+          <t>4158; 13032</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1835; 8178</t>
+          <t>1431; 7762</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1550; 7283</t>
+          <t>0; 4749</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1926; 8977</t>
+          <t>2313; 9811</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4291; 12786</t>
+          <t>6316; 16471</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1947; 8779</t>
+          <t>1842; 8094</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 6015</t>
+          <t>1182; 7427</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5751; 16280</t>
+          <t>5750; 15091</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12402; 25676</t>
+          <t>12027; 26119</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4522; 14070</t>
+          <t>4405; 13500</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2150; 10334</t>
+          <t>1800; 9208</t>
         </is>
       </c>
     </row>
@@ -2415,42 +2415,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2483,42 +2483,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>19374</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>16663</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>21608</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>14720</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>17566</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>17542</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>27899</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>10732</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>19374</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>16663</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>21608</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>15427</t>
+          <t>10912</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>26159</t>
+          <t>25632</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12270; 24850</t>
+          <t>13335; 26496</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11396; 24047</t>
+          <t>10816; 24469</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20620; 37003</t>
+          <t>14667; 28961</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5616; 17270</t>
+          <t>8760; 22683</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13325; 27108</t>
+          <t>12065; 24199</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10476; 23931</t>
+          <t>11854; 24692</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14803; 29262</t>
+          <t>20366; 36021</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9532; 23319</t>
+          <t>6539; 17252</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>28068; 46755</t>
+          <t>28621; 46463</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>26460; 45501</t>
+          <t>25312; 45018</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>40316; 62642</t>
+          <t>39101; 61960</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>17400; 36840</t>
+          <t>18385; 35659</t>
         </is>
       </c>
     </row>
@@ -2623,42 +2623,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>12490</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>20024</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>22141</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>9252</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>11940</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>18065</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>16089</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>5001</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>12490</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>20024</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>22141</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9614</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>14615</t>
+          <t>14557</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>7387; 18555</t>
+          <t>8025; 18594</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>12331; 24861</t>
+          <t>13875; 27656</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10999; 22773</t>
+          <t>15836; 30223</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2081; 10033</t>
+          <t>4911; 16958</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>7517; 18610</t>
+          <t>7493; 18330</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13689; 28355</t>
+          <t>12358; 26085</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15554; 30171</t>
+          <t>10802; 23204</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>4739; 16843</t>
+          <t>2320; 9938</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>17839; 32800</t>
+          <t>18615; 33231</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>29681; 49371</t>
+          <t>29742; 49364</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>28129; 47835</t>
+          <t>29275; 47648</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>8529; 22786</t>
+          <t>8867; 23327</t>
         </is>
       </c>
     </row>
@@ -2831,42 +2831,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2899,42 +2899,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1298</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>8487</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1917</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2257</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>3301</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>1353</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>3191</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1358</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>1298</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>8487</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1917</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2876</t>
+          <t>1433</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>4234</t>
+          <t>3690</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1227; 6924</t>
+          <t>0; 4521</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 4753</t>
+          <t>4711; 13921</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1180; 6673</t>
+          <t>571; 5128</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 4648</t>
+          <t>597; 6422</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 4578</t>
+          <t>1244; 7344</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4622; 13358</t>
+          <t>0; 4362</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>565; 5245</t>
+          <t>1249; 7042</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>501; 9245</t>
+          <t>0; 5284</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1955; 8755</t>
+          <t>2013; 9098</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5404; 15548</t>
+          <t>5540; 15839</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2437; 10392</t>
+          <t>2404; 9188</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1583; 10161</t>
+          <t>1437; 8556</t>
         </is>
       </c>
     </row>
@@ -3039,42 +3039,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>83</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>98</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>43</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,42 +3107,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>48948</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>58309</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>65157</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>39890</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>44752</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>58020</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>65531</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>27909</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>48948</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>58309</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>65157</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>42057</t>
+          <t>27932</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>69965</t>
+          <t>67821</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>34878; 56454</t>
+          <t>38758; 60353</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>45977; 69901</t>
+          <t>46186; 71776</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>54181; 78750</t>
+          <t>53569; 78871</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>20193; 37938</t>
+          <t>29890; 52443</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>39571; 61459</t>
+          <t>35433; 55704</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>47139; 70518</t>
+          <t>47823; 71532</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>53596; 78633</t>
+          <t>53782; 78446</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>31290; 57353</t>
+          <t>19795; 36976</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>78403; 108127</t>
+          <t>80004; 109706</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>99347; 133515</t>
+          <t>101464; 136514</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>113883; 148752</t>
+          <t>112511; 149522</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>55902; 87706</t>
+          <t>55042; 82965</t>
         </is>
       </c>
     </row>
